--- a/trust/all-profiles.xlsx
+++ b/trust/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-27T08:38:34+00:00</t>
+    <t>2026-02-11T14:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/all-profiles.xlsx
+++ b/trust/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="214">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:17:30+00:00</t>
+    <t>2026-04-27T07:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -510,6 +510,10 @@
     <t>SchemeInformation.operatorAddress.id</t>
   </si>
   <si>
+    <t xml:space="preserve">id
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -517,6 +521,10 @@
   </si>
   <si>
     <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>SchemeInformation.operatorAddress.extension</t>
@@ -533,7 +541,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -569,11 +577,11 @@
     <t>Extensions that cannot be ignored even if unrecognized</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -4285,13 +4293,13 @@
         <v>73</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -4342,7 +4350,7 @@
         <v>73</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>74</v>
@@ -4351,7 +4359,7 @@
         <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>73</v>
@@ -4362,14 +4370,14 @@
         <v>140</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" t="s" s="2">
@@ -4388,16 +4396,16 @@
         <v>73</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" t="s" s="2">
@@ -4435,19 +4443,19 @@
         <v>73</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AE27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>74</v>
@@ -4459,7 +4467,7 @@
         <v>73</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28">
@@ -4467,14 +4475,14 @@
         <v>140</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" t="s" s="2">
@@ -4487,25 +4495,25 @@
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q28" t="s" s="2">
         <v>73</v>
@@ -4554,7 +4562,7 @@
         <v>73</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>74</v>
@@ -4566,7 +4574,7 @@
         <v>73</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29">
@@ -4574,10 +4582,10 @@
         <v>140</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -4600,13 +4608,13 @@
         <v>73</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2"/>
@@ -4657,7 +4665,7 @@
         <v>73</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>79</v>
@@ -4677,10 +4685,10 @@
         <v>140</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4703,13 +4711,13 @@
         <v>73</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2"/>
@@ -4760,7 +4768,7 @@
         <v>73</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>74</v>
@@ -4780,10 +4788,10 @@
         <v>140</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -4809,10 +4817,10 @@
         <v>80</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -4863,7 +4871,7 @@
         <v>73</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>79</v>
@@ -4883,10 +4891,10 @@
         <v>140</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -4912,10 +4920,10 @@
         <v>151</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -4966,7 +4974,7 @@
         <v>73</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>79</v>
@@ -4986,10 +4994,10 @@
         <v>140</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5015,10 +5023,10 @@
         <v>151</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -5069,7 +5077,7 @@
         <v>73</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>79</v>
@@ -5089,10 +5097,10 @@
         <v>140</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5118,10 +5126,10 @@
         <v>151</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -5172,7 +5180,7 @@
         <v>73</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>79</v>
@@ -5192,10 +5200,10 @@
         <v>140</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5221,10 +5229,10 @@
         <v>80</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -5275,7 +5283,7 @@
         <v>73</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>79</v>
@@ -5295,10 +5303,10 @@
         <v>140</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5324,10 +5332,10 @@
         <v>151</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -5378,7 +5386,7 @@
         <v>73</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>79</v>
@@ -5398,10 +5406,10 @@
         <v>140</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -5427,10 +5435,10 @@
         <v>146</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -5481,7 +5489,7 @@
         <v>73</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>79</v>
@@ -5501,10 +5509,10 @@
         <v>140</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -5530,10 +5538,10 @@
         <v>80</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -5584,7 +5592,7 @@
         <v>73</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>74</v>
@@ -5604,10 +5612,10 @@
         <v>140</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -5633,10 +5641,10 @@
         <v>110</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -5687,7 +5695,7 @@
         <v>73</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>79</v>
@@ -5707,10 +5715,10 @@
         <v>140</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -5736,10 +5744,10 @@
         <v>110</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -5790,7 +5798,7 @@
         <v>73</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>79</v>
@@ -5810,10 +5818,10 @@
         <v>140</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -5839,10 +5847,10 @@
         <v>151</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
@@ -5893,7 +5901,7 @@
         <v>73</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>74</v>
@@ -5913,10 +5921,10 @@
         <v>140</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -5942,10 +5950,10 @@
         <v>80</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -5996,7 +6004,7 @@
         <v>73</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>74</v>

--- a/trust/all-profiles.xlsx
+++ b/trust/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-07-03T08:24:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -436,14 +436,14 @@
     <t>HCert.-6</t>
   </si>
   <si>
-    <t xml:space="preserve">http://smart.who.int/trust-phw/StructureDefinition/DVC
+    <t xml:space="preserve">http://smart.who.int/trust-phw/StructureDefinition/DVCMin
 </t>
   </si>
   <si>
-    <t>DVC</t>
-  </si>
-  <si>
-    <t>Digital Vaccination Certificate (Proposed)</t>
+    <t>DVCMin</t>
+  </si>
+  <si>
+    <t>Minimal Digital Vaccination Certificate Payload (Proposed)</t>
   </si>
   <si>
     <t>SchemeInformation</t>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F6" s="2"/>
       <c r="G6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>79</v>
@@ -2293,7 +2293,7 @@
         <v>91</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>79</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="F7" s="2"/>
       <c r="G7" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>79</v>
@@ -2396,7 +2396,7 @@
         <v>95</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>79</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F8" s="2"/>
       <c r="G8" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>79</v>
@@ -2499,7 +2499,7 @@
         <v>99</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>79</v>
@@ -3251,7 +3251,7 @@
         <v>74</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>73</v>
@@ -3326,7 +3326,7 @@
         <v>74</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>73</v>
@@ -3354,7 +3354,7 @@
         <v>74</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>73</v>
@@ -3429,7 +3429,7 @@
         <v>74</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>73</v>
@@ -3457,7 +3457,7 @@
         <v>74</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>73</v>
@@ -3532,7 +3532,7 @@
         <v>74</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>73</v>
@@ -3560,7 +3560,7 @@
         <v>74</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>73</v>
@@ -3635,7 +3635,7 @@
         <v>74</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>73</v>

--- a/trust/all-profiles.xlsx
+++ b/trust/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T08:24:29+00:00</t>
+    <t>2026-07-06T11:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/all-profiles.xlsx
+++ b/trust/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="217">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T11:52:41+00:00</t>
+    <t>2026-07-30T11:57:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -444,6 +444,16 @@
   </si>
   <si>
     <t>Minimal Digital Vaccination Certificate Payload (Proposed)</t>
+  </si>
+  <si>
+    <t>HCert.-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://smart.who.int/ph4h/StructureDefinition/MedicationTreatmentLineMin
+</t>
+  </si>
+  <si>
+    <t>Medication Treatment Line Minimal (Proposed)</t>
   </si>
   <si>
     <t>SchemeInformation</t>
@@ -1481,7 +1491,7 @@
         <v>2</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="87">
@@ -1489,7 +1499,7 @@
         <v>4</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="88">
@@ -1505,7 +1515,7 @@
         <v>8</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="90">
@@ -1513,7 +1523,7 @@
         <v>9</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="91">
@@ -1521,7 +1531,7 @@
         <v>11</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92">
@@ -1567,7 +1577,7 @@
         <v>22</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="98">
@@ -1603,7 +1613,7 @@
         <v>30</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="103">
@@ -1637,7 +1647,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.34375" customWidth="true" bestFit="true"/>
@@ -3646,7 +3656,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>140</v>
@@ -3663,7 +3673,7 @@
         <v>74</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>73</v>
@@ -3675,13 +3685,13 @@
         <v>73</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s" s="2">
         <v>142</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -3732,13 +3742,13 @@
         <v>73</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>73</v>
@@ -3749,13 +3759,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -3763,10 +3773,10 @@
       </c>
       <c r="F21" s="2"/>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>73</v>
@@ -3778,10 +3788,10 @@
         <v>73</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>147</v>
@@ -3835,13 +3845,13 @@
         <v>73</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>73</v>
@@ -3852,7 +3862,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>148</v>
@@ -3881,13 +3891,13 @@
         <v>73</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -3955,13 +3965,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -3984,7 +3994,7 @@
         <v>73</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M23" t="s" s="2">
         <v>152</v>
@@ -4041,7 +4051,7 @@
         <v>73</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>79</v>
@@ -4058,7 +4068,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>153</v>
@@ -4087,13 +4097,13 @@
         <v>73</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -4161,13 +4171,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -4178,7 +4188,7 @@
         <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>73</v>
@@ -4190,7 +4200,7 @@
         <v>73</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>157</v>
@@ -4247,30 +4257,30 @@
         <v>73</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>158</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4278,10 +4288,10 @@
       </c>
       <c r="F26" s="2"/>
       <c r="G26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>73</v>
@@ -4293,13 +4303,13 @@
         <v>73</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>161</v>
-      </c>
       <c r="N26" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" s="2"/>
@@ -4350,41 +4360,41 @@
         <v>73</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>73</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>73</v>
@@ -4396,17 +4406,15 @@
         <v>73</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" s="2"/>
       <c r="Q27" t="s" s="2">
         <v>73</v>
@@ -4443,46 +4451,46 @@
         <v>73</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>171</v>
+        <v>73</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>172</v>
+        <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" t="s" s="2">
@@ -4495,26 +4503,24 @@
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="P28" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
         <v>73</v>
       </c>
@@ -4550,19 +4556,19 @@
         <v>73</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="AE28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>74</v>
@@ -4574,26 +4580,26 @@
         <v>73</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>75</v>
@@ -4602,22 +4608,26 @@
         <v>73</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>73</v>
+        <v>181</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>73</v>
+        <v>181</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="P29" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
         <v>73</v>
       </c>
@@ -4665,10 +4675,10 @@
         <v>73</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>75</v>
@@ -4677,12 +4687,12 @@
         <v>73</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>186</v>
@@ -4696,7 +4706,7 @@
       </c>
       <c r="F30" s="2"/>
       <c r="G30" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>75</v>
@@ -4771,7 +4781,7 @@
         <v>186</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>75</v>
@@ -4785,7 +4795,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>189</v>
@@ -4799,10 +4809,10 @@
       </c>
       <c r="F31" s="2"/>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>73</v>
@@ -4814,10 +4824,10 @@
         <v>73</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>191</v>
@@ -4874,10 +4884,10 @@
         <v>189</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>73</v>
@@ -4888,7 +4898,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>192</v>
@@ -4917,13 +4927,13 @@
         <v>73</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="M32" t="s" s="2">
         <v>193</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -4991,13 +5001,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5020,13 +5030,13 @@
         <v>73</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2"/>
@@ -5077,7 +5087,7 @@
         <v>73</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>79</v>
@@ -5094,13 +5104,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5123,13 +5133,13 @@
         <v>73</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2"/>
@@ -5180,7 +5190,7 @@
         <v>73</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>79</v>
@@ -5197,13 +5207,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5226,13 +5236,13 @@
         <v>73</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -5283,7 +5293,7 @@
         <v>73</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>79</v>
@@ -5300,13 +5310,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5329,13 +5339,13 @@
         <v>73</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
@@ -5386,7 +5396,7 @@
         <v>73</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>79</v>
@@ -5403,13 +5413,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -5432,13 +5442,13 @@
         <v>73</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -5489,7 +5499,7 @@
         <v>73</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>79</v>
@@ -5506,13 +5516,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -5520,10 +5530,10 @@
       </c>
       <c r="F38" s="2"/>
       <c r="G38" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>73</v>
@@ -5535,13 +5545,13 @@
         <v>73</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -5592,13 +5602,13 @@
         <v>73</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>73</v>
@@ -5609,13 +5619,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -5623,10 +5633,10 @@
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>73</v>
@@ -5638,13 +5648,13 @@
         <v>73</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -5695,13 +5705,13 @@
         <v>73</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>73</v>
@@ -5712,13 +5722,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -5744,10 +5754,10 @@
         <v>110</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -5798,7 +5808,7 @@
         <v>73</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>79</v>
@@ -5815,13 +5825,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -5829,10 +5839,10 @@
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>73</v>
@@ -5844,13 +5854,13 @@
         <v>73</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
@@ -5901,13 +5911,13 @@
         <v>73</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>73</v>
@@ -5918,13 +5928,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -5947,13 +5957,13 @@
         <v>73</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -6004,7 +6014,7 @@
         <v>73</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>74</v>
@@ -6016,6 +6026,109 @@
         <v>73</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R43" s="2"/>
+      <c r="S43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK43" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/trust/all-profiles.xlsx
+++ b/trust/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.0</t>
+    <t>1.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T11:57:48+00:00</t>
+    <t>2026-08-27T05:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/all-profiles.xlsx
+++ b/trust/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.1</t>
+    <t>1.7.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T05:52:17+00:00</t>
+    <t>2026-09-03T12:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
